--- a/samples/ss_grati_ingest.xlsx
+++ b/samples/ss_grati_ingest.xlsx
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">

--- a/samples/ss_grati_ingest.xlsx
+++ b/samples/ss_grati_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,7 +738,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT 2,3 Grati 500/150 kV</t>
+          <t>IBT 2 Grati 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -775,14 +775,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>IBT 2,3</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -813,31 +809,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grati (bus 150 kV)</t>
+          <t>IBT 3 Grati 500/150 kV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>IBT 3 GRATI7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>GRATI7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>GRATI5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -849,10 +859,14 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -866,12 +880,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gedangan</t>
+          <t>Grati (bus 150 kV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GDTAN</t>
+          <t>GRATI5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -880,7 +894,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -902,14 +916,10 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -923,12 +933,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Probolinggo</t>
+          <t>Gedangan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PBLGO</t>
+          <t>GDTAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -937,7 +947,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -949,11 +959,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>seksi A</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -963,10 +969,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -980,12 +990,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rejoso</t>
+          <t>Probolinggo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RJOSO</t>
+          <t>PBLGO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1006,7 +1016,11 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>seksi A</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
@@ -1033,12 +1047,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PIER</t>
+          <t>Rejoso</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PIER</t>
+          <t>RJOSO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1069,14 +1083,10 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1090,12 +1100,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bangil (bus 150 kV)</t>
+          <t>PIER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BNGIL5</t>
+          <t>PIER</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1104,7 +1114,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1131,7 +1141,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1147,12 +1157,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Purwosari</t>
+          <t>Bangil (bus 150 kV)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PWSRI</t>
+          <t>BNGIL5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1183,10 +1193,14 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1200,12 +1214,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sutami</t>
+          <t>Purwosari</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STAMI</t>
+          <t>PWSRI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1214,7 +1228,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1236,14 +1250,10 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1257,17 +1267,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLTA Sutami</t>
+          <t>Sutami</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KIT_STAMI</t>
+          <t>STAMI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1293,10 +1303,14 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1310,17 +1324,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Bangil</t>
+          <t>PLTA Sutami</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NBNGIL</t>
+          <t>KIT_STAMI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1346,14 +1360,10 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1367,12 +1377,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bacukiro</t>
+          <t>New Bangil</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BCKRO</t>
+          <t>NBNGIL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1403,10 +1413,14 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1420,12 +1434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KIS</t>
+          <t>Bacukiro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KIS</t>
+          <t>BCKRO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1456,14 +1470,10 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1477,12 +1487,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pakis</t>
+          <t>KIS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PAKIS</t>
+          <t>KIS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1513,10 +1523,14 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1530,12 +1544,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wlingi (bus 150 kV)</t>
+          <t>Pakis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WLNGI5</t>
+          <t>PAKIS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1544,7 +1558,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1566,14 +1580,10 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>9;10;15</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1587,12 +1597,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blimbing Kandang</t>
+          <t>Wlingi (bus 150 kV)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BLKND</t>
+          <t>WLNGI5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1628,7 +1638,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9;10;15</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1644,12 +1654,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ngempadan</t>
+          <t>Blimbing Kandang</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NPDAN</t>
+          <t>BLKND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1685,7 +1695,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1701,12 +1711,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ngeprogo</t>
+          <t>Ngempadan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NPROG</t>
+          <t>NPDAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1737,10 +1747,14 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1754,51 +1768,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBT 1,2 Wlingi 150/70 kV</t>
+          <t>Ngeprogo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IBT 1 WLNGI5</t>
+          <t>NPROG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>WLNGI5</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>WLNGI4</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>IBT 1,2</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
@@ -1808,14 +1804,10 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1829,17 +1821,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wlingi (bus 70 kV)</t>
+          <t>IBT 1 Wlingi 150/70 kV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WLNGI4</t>
+          <t>IBT 1 WLNGI5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1847,13 +1839,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>WLNGI5</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>WLNGI4</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -1870,7 +1876,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -1886,17 +1892,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PLTA Wlingi</t>
+          <t>IBT 2 Wlingi 150/70 kV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KIT_WLNGI</t>
+          <t>IBT 2 WLNGI5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1904,13 +1910,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>WLNGI5</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>WLNGI4</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -1922,10 +1942,14 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1939,12 +1963,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lawang</t>
+          <t>Wlingi (bus 70 kV)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LWANG</t>
+          <t>WLNGI4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1957,7 +1981,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1975,10 +1999,14 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1992,21 +2020,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blitar</t>
+          <t>PLTA Wlingi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BLTAR</t>
+          <t>KIT_WLNGI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2028,14 +2056,10 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2049,12 +2073,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kebonagung (bus 150 kV)</t>
+          <t>Lawang</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KBAGN</t>
+          <t>LWANG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2063,7 +2087,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2102,51 +2126,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IBT 1,2,3 Kebonagung 150/70 kV</t>
+          <t>Blitar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IBT 1 KBAGN</t>
+          <t>BLTAR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1,2,3</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>KBAGN</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>KBAGN4</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>IBT 1,2,3</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
@@ -2156,10 +2162,14 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2173,12 +2183,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kebonagung (bus 70 kV)</t>
+          <t>Kebonagung (bus 150 kV)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KBAGN4</t>
+          <t>KBAGN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2187,11 +2197,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -2226,17 +2236,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sekarlangit (bus 150 kV)</t>
+          <t>IBT 1 Kebonagung 150/70 kV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SKLNG5</t>
+          <t>IBT 1 KBAGN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2244,13 +2254,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>KBAGN</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>KBAGN4</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2279,12 +2303,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IBT 1,2 Sekarlangit 150/70 kV</t>
+          <t>IBT 2 Kebonagung 150/70 kV</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IBT 1 SKLNG5</t>
+          <t>IBT 2 KBAGN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2293,7 +2317,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2302,28 +2326,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SKLNG5</t>
+          <t>KBAGN</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SKLNG4</t>
+          <t>KBAGN4</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>IBT 1,2</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
@@ -2333,14 +2353,10 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2354,31 +2370,45 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sekarlangit (bus 70 kV)</t>
+          <t>IBT 3 Kebonagung 150/70 kV</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SKLNG4</t>
+          <t>IBT 3 KBAGN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>KBAGN</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>KBAGN4</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2407,12 +2437,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Turen</t>
+          <t>Kebonagung (bus 70 kV)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TUREN</t>
+          <t>KBAGN4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2421,7 +2451,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2443,14 +2473,10 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2464,12 +2490,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sengguruh</t>
+          <t>Sekarlangit (bus 150 kV)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SGRUH</t>
+          <t>SKLNG5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2478,11 +2504,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2517,17 +2543,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PLTA Sengguruh</t>
+          <t>IBT 1 Sekarlangit 150/70 kV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KIT_SGRUH</t>
+          <t>IBT 1 SKLNG5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2535,13 +2561,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SKLNG5</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SKLNG4</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2553,10 +2593,14 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2570,17 +2614,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pulahan</t>
+          <t>IBT 2 Sekarlangit 150/70 kV</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PLHAN</t>
+          <t>IBT 2 SKLNG5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2588,13 +2632,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SKLNG5</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SKLNG4</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2606,10 +2664,14 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2623,12 +2685,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mendalan</t>
+          <t>Sekarlangit (bus 70 kV)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MDLAN</t>
+          <t>SKLNG4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2659,14 +2721,10 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2680,17 +2738,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PLTA Selorejo</t>
+          <t>Turen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KIT_SLRJO</t>
+          <t>TUREN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2716,10 +2774,14 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2733,12 +2795,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gondang Pagan</t>
+          <t>Sengguruh</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GPGAN</t>
+          <t>SGRUH</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2747,7 +2809,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2769,14 +2831,10 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>15;16</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2790,21 +2848,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Karangkates</t>
+          <t>PLTA Sengguruh</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KKTES</t>
+          <t>KIT_SGRUH</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2826,14 +2884,10 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2847,12 +2901,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Balebang</t>
+          <t>Pulahan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BLBNG</t>
+          <t>PLHAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2861,7 +2915,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2873,11 +2927,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>seksi A/B</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
@@ -2904,12 +2954,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Siman</t>
+          <t>Mendalan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SIMAN</t>
+          <t>MDLAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2918,7 +2968,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2940,10 +2990,14 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2957,21 +3011,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sukorejo (bus 70 kV)</t>
+          <t>PLTA Selorejo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SKTIH4</t>
+          <t>KIT_SLRJO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2983,22 +3037,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Kediri</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -3011,6 +3057,291 @@
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gondang Pagan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GPGAN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>15;16</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Karangkates</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>KKTES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Balebang</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BLBNG</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>seksi A/B</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Siman</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SIMAN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sukorejo (bus 70 kV)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SKTIH4</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Kediri</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5427,12 +5758,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] GI 150 kV PLTASutami hanyasingleBusbar</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV PLTASutami hanyasingleBusbar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5462,12 +5793,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] SUTT 150 kV Wlingi- Sutami hanya beroperasi1sirkitdan sudahberbebandiatas 95%</t>
+          <t>[BELUM_DITETAPKAN] SUTT 150 kV Wlingi- Sutami hanya beroperasi1sirkitdan sudahberbebandiatas 95%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5497,12 +5828,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[N-1] GI 150 kV dan 70 kV PLTA Wlingi hanya singleBusbar</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV dan 70 kV PLTA Wlingi hanya singleBusbar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5532,12 +5863,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan IBT 150/70 kV GI Wlingi sudah &gt;90% dan hanya ada satu IBT, sehingga apabila terjadi gangguan pada IBT tersebut maka akan terjadi pemadaman dan sulit untuk melakukan pemeliharaan</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan IBT 150/70 kV GI Wlingi sudah &gt;90% dan hanya ada satu IBT, sehingga apabila terjadi gangguan pada IBT tersebut maka akan terjadi pemadaman dan sulit untuk melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5672,12 +6003,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[N-1] GI 70 kV Turen, GI 70 kV Sengguruh, GI 70 kV PLTA Selorejo, GI 70 kV Gampingan, GI 70 kV Karangkates, GI 70 kV Siman hanya beroperasi single Busbar</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV Turen, GI 70 kV Sengguruh, GI 70 kV PLTA Selorejo, GI 70 kV Gampingan, GI 70 kV Karangkates, GI 70 kV Siman hanya beroperasi single Busbar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5707,12 +6038,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi Drop tegangan di Subsistem Grati pada GI 150 kVSutami, GIWlingidan GI 70 kV Gampingan</t>
+          <t>[BELUM_DITETAPKAN] Terjadi Drop tegangan di Subsistem Grati pada GI 150 kVSutami, GIWlingidan GI 70 kV Gampingan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
